--- a/artfynd/A 50437-2025 artfynd.xlsx
+++ b/artfynd/A 50437-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130015680</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,6 +892,224 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130052062</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96394</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Älgö, Älgö, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>281877</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6529715</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tjärnö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna  Hansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna  Hansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130052577</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Älgö, Älgö, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>281901</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6529799</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tjärnö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna  Hansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna  Hansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50437-2025 artfynd.xlsx
+++ b/artfynd/A 50437-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>130052577</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50437-2025 artfynd.xlsx
+++ b/artfynd/A 50437-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130015680</v>
+        <v>130015971</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älgö, Älgö, Boh</t>
+          <t>Älgö, Älgöleran, Strömstad, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>281897</v>
+        <v>281991</v>
       </c>
       <c r="R2" t="n">
-        <v>6529797</v>
+        <v>6529831</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +787,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130015971</v>
+        <v>130052062</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>96411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>49</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Älgö, Älgöleran, Strömstad, Boh</t>
+          <t>Älgö, Älgö, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>281991</v>
+        <v>281877</v>
       </c>
       <c r="R3" t="n">
-        <v>6529831</v>
+        <v>6529715</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,22 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,52 +898,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130052062</v>
+        <v>130052577</v>
       </c>
       <c r="B4" t="n">
-        <v>96394</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älgö, Älgö, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>281877</v>
+        <v>281901</v>
       </c>
       <c r="R4" t="n">
-        <v>6529715</v>
+        <v>6529799</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,113 +1002,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>130052577</v>
-      </c>
-      <c r="B5" t="n">
-        <v>79089</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Älgö, Älgö, Boh</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>281901</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6529799</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Strömstad</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Tjärnö</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Anna  Hansson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Anna  Hansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50437-2025 artfynd.xlsx
+++ b/artfynd/A 50437-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130052062</v>
       </c>
       <c r="B3" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50437-2025 artfynd.xlsx
+++ b/artfynd/A 50437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130015971</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130052062</v>
       </c>
       <c r="B3" t="n">
-        <v>96429</v>
+        <v>96516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50437-2025 artfynd.xlsx
+++ b/artfynd/A 50437-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>130312090</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50437-2025 artfynd.xlsx
+++ b/artfynd/A 50437-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>130312090</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50437-2025 artfynd.xlsx
+++ b/artfynd/A 50437-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>130312090</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50437-2025 artfynd.xlsx
+++ b/artfynd/A 50437-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>130312090</v>
       </c>
       <c r="B4" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50437-2025 artfynd.xlsx
+++ b/artfynd/A 50437-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>130312090</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50437-2025 artfynd.xlsx
+++ b/artfynd/A 50437-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130051324</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130052062</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130015971</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130312090</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,8 +1265,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130312918</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>